--- a/sitepreview/ddcc/1.0.0/StructureDefinition-DDCCGenerateHealthCertificateParameters.xlsx
+++ b/sitepreview/ddcc/1.0.0/StructureDefinition-DDCCGenerateHealthCertificateParameters.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-15T09:19:12+00:00</t>
+    <t>2024-10-17T05:06:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sitepreview/ddcc/1.0.0/StructureDefinition-DDCCGenerateHealthCertificateParameters.xlsx
+++ b/sitepreview/ddcc/1.0.0/StructureDefinition-DDCCGenerateHealthCertificateParameters.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T05:06:50+00:00</t>
+    <t>2024-10-17T05:25:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sitepreview/ddcc/1.0.0/StructureDefinition-DDCCGenerateHealthCertificateParameters.xlsx
+++ b/sitepreview/ddcc/1.0.0/StructureDefinition-DDCCGenerateHealthCertificateParameters.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T05:25:33+00:00</t>
+    <t>2024-10-17T06:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
